--- a/artfynd/A 22225-2025 artfynd.xlsx
+++ b/artfynd/A 22225-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113459712</v>
+        <v>127837941</v>
       </c>
       <c r="B2" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106061</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>221101</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,21 +704,23 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Granhagen, Vg</t>
+          <t>Korsbacka/bäcken, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>405563</v>
+        <v>405491</v>
       </c>
       <c r="R2" t="n">
-        <v>6403580</v>
+        <v>6403491</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,12 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-05-20</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-05-20</t>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Plantor på ömse sidor om bäcken och bron, allra flest till sydväst, där stod säkert ett hundratal. Alla i pågående samtidig blomning och fruktsättning som Impatiens plägar göra.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,23 +767,123 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Tina Kyrkander</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Lars Berglund</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Lars Berglund</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>113459711</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Granhagen, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>405563</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6403580</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ulricehamn</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Marbäck</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-05-20</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-05-20</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Tina Kyrkander</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Louise Säf</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Tina Kyrkander</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Artinventering Granhagen 2023</t>
         </is>

--- a/artfynd/A 22225-2025 artfynd.xlsx
+++ b/artfynd/A 22225-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127837941</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,8 +898,17 @@
           <t>Artinventering Granhagen 2023</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113459711</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>